--- a/data/trans_orig/P34B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población camina durante más de 30 minutos</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población camina (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,74</t>
+          <t>1,3; 1,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,2</t>
+          <t>2,6; 3,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,99</t>
+          <t>2,99; 3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 2,7</t>
+          <t>2,17; 2,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,5</t>
+          <t>2,95; 3,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,02</t>
+          <t>3,16; 4,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,26</t>
+          <t>2,85; 3,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,85</t>
+          <t>3,2; 3,85</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,14</t>
+          <t>1,73; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,55</t>
+          <t>3,04; 3,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,9</t>
+          <t>3,19; 3,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 3,24</t>
+          <t>2,73; 3,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 3,62</t>
+          <t>3,13; 3,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,89</t>
+          <t>2,85; 3,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,57</t>
+          <t>2,26; 2,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,52</t>
+          <t>3,16; 3,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,77</t>
+          <t>3,13; 3,77</t>
         </is>
       </c>
     </row>
@@ -897,27 +897,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,55</t>
+          <t>2,1; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,16</t>
+          <t>2,71; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 3,91</t>
+          <t>3,37; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,09</t>
+          <t>2,65; 3,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,48</t>
+          <t>3,06; 3,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,77</t>
+          <t>2,44; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,25</t>
+          <t>2,92; 3,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 3,77</t>
+          <t>3,45; 3,77</t>
         </is>
       </c>
     </row>
@@ -1007,22 +1007,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 2,94</t>
+          <t>2,47; 2,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,51</t>
+          <t>3,0; 3,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,94</t>
+          <t>1,87; 3,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,3</t>
+          <t>2,84; 3,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1032,22 +1032,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 3,8</t>
+          <t>2,89; 3,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,05</t>
+          <t>2,71; 3,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,48</t>
+          <t>3,15; 3,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,78</t>
+          <t>2,39; 3,76</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 3,87</t>
+          <t>3,28; 3,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,03</t>
+          <t>3,51; 4,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,06</t>
+          <t>3,63; 4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,58</t>
+          <t>3,02; 3,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 3,32</t>
+          <t>2,77; 3,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 3,9</t>
+          <t>3,53; 3,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 3,63</t>
+          <t>3,24; 3,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,57</t>
+          <t>3,19; 3,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 3,93</t>
+          <t>3,63; 3,93</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 4,47</t>
+          <t>3,82; 4,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,29</t>
+          <t>3,63; 4,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 4,86</t>
+          <t>4,37; 4,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,38</t>
+          <t>2,75; 3,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,5</t>
+          <t>2,87; 3,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 3,82</t>
+          <t>3,2; 3,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 3,81</t>
+          <t>3,34; 3,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 3,79</t>
+          <t>3,34; 3,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,19</t>
+          <t>3,45; 4,2</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1337,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,21</t>
+          <t>3,44; 4,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,73</t>
+          <t>3,03; 3,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,16</t>
+          <t>3,61; 4,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,27 +1357,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,65</t>
+          <t>2,06; 2,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,54</t>
+          <t>2,15; 2,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,14</t>
+          <t>2,63; 3,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 2,96</t>
+          <t>2,48; 3,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 3,14</t>
+          <t>2,79; 3,15</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,54; 2,75</t>
+          <t>2,53; 2,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,4</t>
+          <t>3,21; 3,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,24</t>
+          <t>3,05; 3,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 3,54</t>
+          <t>3,3; 3,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,3</t>
+          <t>3,15; 3,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,64</t>
+          <t>3,18; 3,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Edad-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,77</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>3,75</t>
         </is>
       </c>
     </row>
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,74</t>
+          <t>1,28; 1,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,17</t>
+          <t>2,61; 3,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,98</t>
+          <t>3,27; 4,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,68</t>
+          <t>2,18; 2,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,01</t>
+          <t>3,29; 4,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,12</t>
+          <t>1,78; 2,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,23</t>
+          <t>2,84; 3,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,85</t>
+          <t>3,41; 4,04</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,78</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,13</t>
+          <t>1,73; 2,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,54</t>
+          <t>3,07; 3,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 3,9</t>
+          <t>3,37; 4,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,22</t>
+          <t>2,72; 3,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 3,58</t>
+          <t>3,13; 3,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,86</t>
+          <t>3,53; 4,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 2,58</t>
+          <t>2,27; 2,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,52</t>
+          <t>3,18; 3,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 3,77</t>
+          <t>3,57; 3,99</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,65</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 2,54</t>
+          <t>2,13; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,16</t>
+          <t>2,7; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 3,88</t>
+          <t>3,41; 3,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,05</t>
+          <t>2,66; 3,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,5</t>
+          <t>3,04; 3,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 3,81</t>
+          <t>3,45; 3,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 2,76</t>
+          <t>2,44; 2,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,23</t>
+          <t>2,94; 3,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 3,77</t>
+          <t>3,49; 3,8</t>
         </is>
       </c>
     </row>
@@ -964,14 +964,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>3,87</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,06</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,37</t>
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 2,98</t>
+          <t>2,47; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,5</t>
+          <t>3,03; 3,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,92</t>
+          <t>3,66; 4,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,3</t>
+          <t>2,84; 3,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,6</t>
+          <t>3,15; 3,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,79</t>
+          <t>3,62; 3,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,04</t>
+          <t>2,71; 3,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,49</t>
+          <t>3,16; 3,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,76</t>
+          <t>3,68; 3,95</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>3,8</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 3,91</t>
+          <t>3,31; 3,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,07</t>
+          <t>3,5; 4,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,06</t>
+          <t>3,65; 4,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,56</t>
+          <t>3,0; 3,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,27</t>
+          <t>2,76; 3,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 3,91</t>
+          <t>3,54; 3,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 3,64</t>
+          <t>3,23; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 3,59</t>
+          <t>3,21; 3,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 3,93</t>
+          <t>3,66; 3,94</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,16</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,82; 4,45</t>
+          <t>3,78; 4,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,28</t>
+          <t>3,61; 4,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 4,81</t>
+          <t>4,35; 4,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 3,35</t>
+          <t>2,76; 3,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,5</t>
+          <t>2,92; 3,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 3,82</t>
+          <t>3,54; 3,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 3,8</t>
+          <t>3,32; 3,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 3,79</t>
+          <t>3,34; 3,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 4,2</t>
+          <t>4,01; 4,31</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1337,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,23</t>
+          <t>3,45; 4,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,67</t>
+          <t>3,0; 3,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 4,21</t>
+          <t>3,63; 4,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1357,27 +1357,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,68</t>
+          <t>2,02; 2,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,54</t>
+          <t>2,16; 2,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,12</t>
+          <t>2,65; 3,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,0</t>
+          <t>2,49; 2,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 3,15</t>
+          <t>2,81; 3,14</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,72</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1447,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 2,74</t>
+          <t>2,54; 2,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,41</t>
+          <t>3,2; 3,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,86</t>
+          <t>3,79; 4,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,97</t>
+          <t>2,77; 2,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,53</t>
+          <t>3,49; 3,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,29</t>
+          <t>3,16; 3,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,65</t>
+          <t>3,65; 3,79</t>
         </is>
       </c>
     </row>
